--- a/data/historico/semana_322.xlsx
+++ b/data/historico/semana_322.xlsx
@@ -30,8 +30,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 20min'!$A$2:$J$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$105</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$H$42</definedName>
   </definedNames>
@@ -5299,7 +5299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5311,7 +5311,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (4 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (5 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="B5" s="37" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="C5" s="37" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
@@ -5428,8 +5428,30 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="37" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="37" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:D6"/>
+  <autoFilter ref="A2:D7"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -7544,7 +7566,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>2</v>
@@ -7576,7 +7598,7 @@
         <v>5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>2</v>
@@ -7608,7 +7630,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>2</v>
@@ -7672,7 +7694,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>2</v>
@@ -7704,7 +7726,7 @@
         <v>5</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>2</v>
@@ -7736,7 +7758,7 @@
         <v>5</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>2</v>
@@ -7768,7 +7790,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>1</v>
@@ -7800,7 +7822,7 @@
         <v>5</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>2</v>
@@ -7832,7 +7854,7 @@
         <v>5</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>1</v>
@@ -7864,7 +7886,7 @@
         <v>5</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>2</v>
@@ -7896,7 +7918,7 @@
         <v>5</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>2</v>
@@ -7928,7 +7950,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>3</v>
@@ -7960,7 +7982,7 @@
         <v>3</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>5</v>
@@ -7992,7 +8014,7 @@
         <v>5</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>2</v>
@@ -8024,7 +8046,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>2</v>
@@ -8056,7 +8078,7 @@
         <v>5</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>2</v>
@@ -8088,7 +8110,7 @@
         <v>5</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>3</v>
@@ -8120,7 +8142,7 @@
         <v>5</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>2</v>
@@ -8152,7 +8174,7 @@
         <v>5</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>2</v>
@@ -8184,7 +8206,7 @@
         <v>5</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>1</v>
@@ -8216,7 +8238,7 @@
         <v>3</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>4</v>
@@ -8248,7 +8270,7 @@
         <v>5</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>1</v>
@@ -8280,7 +8302,7 @@
         <v>4</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>3</v>
@@ -8312,7 +8334,7 @@
         <v>3</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>3</v>
@@ -8332,25 +8354,25 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>84.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
@@ -8364,25 +8386,25 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>84.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
@@ -8396,7 +8418,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -8405,16 +8427,16 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>84.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
@@ -8428,25 +8450,25 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>84</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
@@ -8460,25 +8482,25 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>82.3</v>
+        <v>84</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
@@ -8492,25 +8514,25 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>81.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
@@ -8524,25 +8546,25 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>81.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
@@ -8556,25 +8578,25 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>79.8</v>
+        <v>81.2</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
@@ -8600,7 +8622,7 @@
         <v>5</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>3</v>
@@ -8632,7 +8654,7 @@
         <v>3</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>4</v>
@@ -8664,7 +8686,7 @@
         <v>4</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>4</v>
@@ -8696,7 +8718,7 @@
         <v>5</v>
       </c>
       <c r="E39" s="34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F39" s="34" t="n">
         <v>3</v>
@@ -8728,7 +8750,7 @@
         <v>3</v>
       </c>
       <c r="E40" s="34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F40" s="34" t="n">
         <v>4</v>
@@ -8760,7 +8782,7 @@
         <v>5</v>
       </c>
       <c r="E41" s="34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F41" s="34" t="n">
         <v>2</v>
@@ -8792,7 +8814,7 @@
         <v>4</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>3</v>
@@ -14051,7 +14073,7 @@
         </is>
       </c>
       <c r="D208" s="46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E208" s="46" t="n">
         <v>1.5</v>
@@ -14063,7 +14085,7 @@
         <v>3</v>
       </c>
       <c r="H208" s="46" t="n">
-        <v>-12</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="209">
@@ -21799,7 +21821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -21814,7 +21836,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (103 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
+          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (101 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -24208,11 +24230,11 @@
     </row>
     <row r="70">
       <c r="A70" s="35" t="n">
-        <v>2721</v>
+        <v>3038</v>
       </c>
       <c r="B70" s="35" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C70" s="35" t="inlineStr">
@@ -24243,11 +24265,11 @@
     </row>
     <row r="71">
       <c r="A71" s="35" t="n">
-        <v>3038</v>
+        <v>3128</v>
       </c>
       <c r="B71" s="35" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C71" s="35" t="inlineStr">
@@ -24278,11 +24300,11 @@
     </row>
     <row r="72">
       <c r="A72" s="35" t="n">
-        <v>3128</v>
+        <v>113</v>
       </c>
       <c r="B72" s="35" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C72" s="35" t="inlineStr">
@@ -24313,11 +24335,11 @@
     </row>
     <row r="73">
       <c r="A73" s="35" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B73" s="35" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C73" s="35" t="inlineStr">
@@ -24337,7 +24359,7 @@
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G73" s="35" t="inlineStr">
@@ -24348,11 +24370,11 @@
     </row>
     <row r="74">
       <c r="A74" s="35" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B74" s="35" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C74" s="35" t="inlineStr">
@@ -24383,11 +24405,11 @@
     </row>
     <row r="75">
       <c r="A75" s="35" t="n">
-        <v>2721</v>
+        <v>1938</v>
       </c>
       <c r="B75" s="35" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C75" s="35" t="inlineStr">
@@ -24397,17 +24419,17 @@
       </c>
       <c r="D75" s="35" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E75" s="35" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G75" s="35" t="inlineStr">
@@ -24418,11 +24440,11 @@
     </row>
     <row r="76">
       <c r="A76" s="35" t="n">
-        <v>113</v>
+        <v>2721</v>
       </c>
       <c r="B76" s="35" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C76" s="35" t="inlineStr">
@@ -24432,17 +24454,17 @@
       </c>
       <c r="D76" s="35" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E76" s="35" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F76" s="35" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G76" s="35" t="inlineStr">
@@ -24453,11 +24475,11 @@
     </row>
     <row r="77">
       <c r="A77" s="35" t="n">
-        <v>1938</v>
+        <v>2918</v>
       </c>
       <c r="B77" s="35" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C77" s="35" t="inlineStr">
@@ -24477,7 +24499,7 @@
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G77" s="35" t="inlineStr">
@@ -24488,26 +24510,26 @@
     </row>
     <row r="78">
       <c r="A78" s="35" t="n">
-        <v>2721</v>
+        <v>80</v>
       </c>
       <c r="B78" s="35" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C78" s="35" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D78" s="35" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E78" s="35" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F78" s="35" t="inlineStr">
@@ -24523,31 +24545,31 @@
     </row>
     <row r="79">
       <c r="A79" s="35" t="n">
-        <v>2918</v>
+        <v>2789</v>
       </c>
       <c r="B79" s="35" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C79" s="35" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D79" s="35" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E79" s="35" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F79" s="35" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G79" s="35" t="inlineStr">
@@ -24558,11 +24580,11 @@
     </row>
     <row r="80">
       <c r="A80" s="35" t="n">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="B80" s="35" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C80" s="35" t="inlineStr">
@@ -24593,11 +24615,11 @@
     </row>
     <row r="81">
       <c r="A81" s="35" t="n">
-        <v>2789</v>
+        <v>1942</v>
       </c>
       <c r="B81" s="35" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C81" s="35" t="inlineStr">
@@ -24628,11 +24650,11 @@
     </row>
     <row r="82">
       <c r="A82" s="35" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B82" s="35" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C82" s="35" t="inlineStr">
@@ -24663,11 +24685,11 @@
     </row>
     <row r="83">
       <c r="A83" s="35" t="n">
-        <v>1942</v>
+        <v>1996</v>
       </c>
       <c r="B83" s="35" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C83" s="35" t="inlineStr">
@@ -24698,11 +24720,11 @@
     </row>
     <row r="84">
       <c r="A84" s="35" t="n">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="B84" s="35" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C84" s="35" t="inlineStr">
@@ -24733,11 +24755,11 @@
     </row>
     <row r="85">
       <c r="A85" s="35" t="n">
-        <v>1996</v>
+        <v>157</v>
       </c>
       <c r="B85" s="35" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C85" s="35" t="inlineStr">
@@ -24768,11 +24790,11 @@
     </row>
     <row r="86">
       <c r="A86" s="35" t="n">
-        <v>86</v>
+        <v>2789</v>
       </c>
       <c r="B86" s="35" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C86" s="35" t="inlineStr">
@@ -24792,7 +24814,7 @@
       </c>
       <c r="F86" s="35" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G86" s="35" t="inlineStr">
@@ -24803,11 +24825,11 @@
     </row>
     <row r="87">
       <c r="A87" s="35" t="n">
-        <v>157</v>
+        <v>1942</v>
       </c>
       <c r="B87" s="35" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C87" s="35" t="inlineStr">
@@ -24827,7 +24849,7 @@
       </c>
       <c r="F87" s="35" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G87" s="35" t="inlineStr">
@@ -24838,11 +24860,11 @@
     </row>
     <row r="88">
       <c r="A88" s="35" t="n">
-        <v>2789</v>
+        <v>161</v>
       </c>
       <c r="B88" s="35" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C88" s="35" t="inlineStr">
@@ -24873,11 +24895,11 @@
     </row>
     <row r="89">
       <c r="A89" s="35" t="n">
-        <v>1942</v>
+        <v>110</v>
       </c>
       <c r="B89" s="35" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C89" s="35" t="inlineStr">
@@ -24887,17 +24909,17 @@
       </c>
       <c r="D89" s="35" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E89" s="35" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F89" s="35" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G89" s="35" t="inlineStr">
@@ -24908,11 +24930,11 @@
     </row>
     <row r="90">
       <c r="A90" s="35" t="n">
-        <v>161</v>
+        <v>1943</v>
       </c>
       <c r="B90" s="35" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C90" s="35" t="inlineStr">
@@ -24922,17 +24944,17 @@
       </c>
       <c r="D90" s="35" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E90" s="35" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F90" s="35" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G90" s="35" t="inlineStr">
@@ -24943,11 +24965,11 @@
     </row>
     <row r="91">
       <c r="A91" s="35" t="n">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="B91" s="35" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C91" s="35" t="inlineStr">
@@ -24978,11 +25000,11 @@
     </row>
     <row r="92">
       <c r="A92" s="35" t="n">
-        <v>1943</v>
+        <v>110</v>
       </c>
       <c r="B92" s="35" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C92" s="35" t="inlineStr">
@@ -24992,12 +25014,12 @@
       </c>
       <c r="D92" s="35" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E92" s="35" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F92" s="35" t="inlineStr">
@@ -25013,11 +25035,11 @@
     </row>
     <row r="93">
       <c r="A93" s="35" t="n">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="B93" s="35" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C93" s="35" t="inlineStr">
@@ -25027,12 +25049,12 @@
       </c>
       <c r="D93" s="35" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E93" s="35" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F93" s="35" t="inlineStr">
@@ -25048,11 +25070,11 @@
     </row>
     <row r="94">
       <c r="A94" s="35" t="n">
-        <v>110</v>
+        <v>2789</v>
       </c>
       <c r="B94" s="35" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C94" s="35" t="inlineStr">
@@ -25083,11 +25105,11 @@
     </row>
     <row r="95">
       <c r="A95" s="35" t="n">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="B95" s="35" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C95" s="35" t="inlineStr">
@@ -25118,11 +25140,11 @@
     </row>
     <row r="96">
       <c r="A96" s="35" t="n">
-        <v>2789</v>
+        <v>1942</v>
       </c>
       <c r="B96" s="35" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C96" s="35" t="inlineStr">
@@ -25153,11 +25175,11 @@
     </row>
     <row r="97">
       <c r="A97" s="35" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B97" s="35" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C97" s="35" t="inlineStr">
@@ -25188,11 +25210,11 @@
     </row>
     <row r="98">
       <c r="A98" s="35" t="n">
-        <v>1942</v>
+        <v>1996</v>
       </c>
       <c r="B98" s="35" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C98" s="35" t="inlineStr">
@@ -25223,11 +25245,11 @@
     </row>
     <row r="99">
       <c r="A99" s="35" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B99" s="35" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C99" s="35" t="inlineStr">
@@ -25258,11 +25280,11 @@
     </row>
     <row r="100">
       <c r="A100" s="35" t="n">
-        <v>1996</v>
+        <v>1943</v>
       </c>
       <c r="B100" s="35" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C100" s="35" t="inlineStr">
@@ -25282,7 +25304,7 @@
       </c>
       <c r="F100" s="35" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G100" s="35" t="inlineStr">
@@ -25293,11 +25315,11 @@
     </row>
     <row r="101">
       <c r="A101" s="35" t="n">
-        <v>157</v>
+        <v>2789</v>
       </c>
       <c r="B101" s="35" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C101" s="35" t="inlineStr">
@@ -25317,7 +25339,7 @@
       </c>
       <c r="F101" s="35" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G101" s="35" t="inlineStr">
@@ -25328,11 +25350,11 @@
     </row>
     <row r="102">
       <c r="A102" s="35" t="n">
-        <v>1943</v>
+        <v>161</v>
       </c>
       <c r="B102" s="35" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C102" s="35" t="inlineStr">
@@ -25363,11 +25385,11 @@
     </row>
     <row r="103">
       <c r="A103" s="35" t="n">
-        <v>2789</v>
+        <v>157</v>
       </c>
       <c r="B103" s="35" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C103" s="35" t="inlineStr">
@@ -25377,17 +25399,17 @@
       </c>
       <c r="D103" s="35" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E103" s="35" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F103" s="35" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G103" s="35" t="inlineStr">
@@ -25396,78 +25418,8 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="35" t="n">
-        <v>161</v>
-      </c>
-      <c r="B104" s="35" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="C104" s="35" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D104" s="35" t="inlineStr">
-        <is>
-          <t>04/09/2026</t>
-        </is>
-      </c>
-      <c r="E104" s="35" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F104" s="35" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G104" s="35" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="35" t="n">
-        <v>157</v>
-      </c>
-      <c r="B105" s="35" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="C105" s="35" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D105" s="35" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="E105" s="35" t="inlineStr">
-        <is>
-          <t>Segunda</t>
-        </is>
-      </c>
-      <c r="F105" s="35" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G105" s="35" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G105"/>
+  <autoFilter ref="A2:G103"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/data/historico/semana_322.xlsx
+++ b/data/historico/semana_322.xlsx
@@ -7598,7 +7598,7 @@
         <v>5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>2</v>
@@ -7630,7 +7630,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>2</v>
@@ -7662,7 +7662,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>1</v>
@@ -7694,7 +7694,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>2</v>
@@ -7726,7 +7726,7 @@
         <v>5</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>2</v>
@@ -7758,7 +7758,7 @@
         <v>5</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>2</v>
@@ -7822,7 +7822,7 @@
         <v>5</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>2</v>
@@ -7886,7 +7886,7 @@
         <v>5</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>2</v>
@@ -7918,7 +7918,7 @@
         <v>5</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>2</v>
@@ -7950,7 +7950,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>3</v>
@@ -7982,7 +7982,7 @@
         <v>3</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>5</v>
@@ -8014,7 +8014,7 @@
         <v>5</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>2</v>
@@ -8078,7 +8078,7 @@
         <v>5</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>2</v>
@@ -8110,7 +8110,7 @@
         <v>5</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>3</v>
@@ -8142,7 +8142,7 @@
         <v>5</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>2</v>
@@ -8174,7 +8174,7 @@
         <v>5</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>2</v>
@@ -8270,7 +8270,7 @@
         <v>5</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>1</v>
@@ -8302,7 +8302,7 @@
         <v>4</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>3</v>
@@ -8366,7 +8366,7 @@
         <v>4</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>2</v>
@@ -8398,7 +8398,7 @@
         <v>5</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>3</v>
@@ -8430,7 +8430,7 @@
         <v>4</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>2</v>
@@ -8462,7 +8462,7 @@
         <v>5</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>3</v>
@@ -8526,7 +8526,7 @@
         <v>3</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>2</v>
@@ -8558,7 +8558,7 @@
         <v>4</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>6</v>
@@ -8590,7 +8590,7 @@
         <v>3</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>2</v>
@@ -8622,7 +8622,7 @@
         <v>5</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>3</v>
@@ -8654,7 +8654,7 @@
         <v>3</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>4</v>
@@ -8686,7 +8686,7 @@
         <v>4</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>4</v>
@@ -8750,7 +8750,7 @@
         <v>3</v>
       </c>
       <c r="E40" s="34" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F40" s="34" t="n">
         <v>4</v>
@@ -8814,7 +8814,7 @@
         <v>4</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>3</v>

--- a/data/historico/semana_322.xlsx
+++ b/data/historico/semana_322.xlsx
@@ -7566,7 +7566,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>2</v>
@@ -7662,7 +7662,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>1</v>
@@ -7694,7 +7694,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>2</v>
@@ -7758,7 +7758,7 @@
         <v>5</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>2</v>
@@ -7790,7 +7790,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>1</v>
@@ -7854,7 +7854,7 @@
         <v>5</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>1</v>
@@ -7886,7 +7886,7 @@
         <v>5</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>2</v>
@@ -7982,7 +7982,7 @@
         <v>3</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>5</v>
@@ -8046,7 +8046,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>2</v>
@@ -8110,7 +8110,7 @@
         <v>5</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>3</v>
@@ -8142,7 +8142,7 @@
         <v>5</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>2</v>
@@ -8174,7 +8174,7 @@
         <v>5</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>2</v>
@@ -8206,7 +8206,7 @@
         <v>5</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>1</v>
@@ -8238,7 +8238,7 @@
         <v>3</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>4</v>
@@ -8270,7 +8270,7 @@
         <v>5</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>1</v>
@@ -8334,7 +8334,7 @@
         <v>3</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>3</v>
@@ -8366,7 +8366,7 @@
         <v>4</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>2</v>
@@ -8398,7 +8398,7 @@
         <v>5</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>3</v>
@@ -8494,7 +8494,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>4</v>
@@ -8526,7 +8526,7 @@
         <v>3</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>2</v>
@@ -8558,7 +8558,7 @@
         <v>4</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>6</v>
@@ -8590,7 +8590,7 @@
         <v>3</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>2</v>
@@ -8622,7 +8622,7 @@
         <v>5</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>3</v>
@@ -8654,7 +8654,7 @@
         <v>3</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>4</v>
@@ -8686,7 +8686,7 @@
         <v>4</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>4</v>
@@ -8718,7 +8718,7 @@
         <v>5</v>
       </c>
       <c r="E39" s="34" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F39" s="34" t="n">
         <v>3</v>
@@ -8750,7 +8750,7 @@
         <v>3</v>
       </c>
       <c r="E40" s="34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F40" s="34" t="n">
         <v>4</v>
@@ -8782,7 +8782,7 @@
         <v>5</v>
       </c>
       <c r="E41" s="34" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F41" s="34" t="n">
         <v>2</v>
@@ -8814,7 +8814,7 @@
         <v>4</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>3</v>

--- a/data/historico/semana_322.xlsx
+++ b/data/historico/semana_322.xlsx
@@ -7918,7 +7918,7 @@
         <v>5</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>2</v>
@@ -8078,7 +8078,7 @@
         <v>5</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>2</v>
@@ -8814,7 +8814,7 @@
         <v>4</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>3</v>
